--- a/data/cache/vbma.xlsx
+++ b/data/cache/vbma.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-06T09:15:11+00:00</t>
+          <t>2026-10-09T15:29:41+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -524,7 +524,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-06T09:15:11+00:00</t>
+          <t>2026-10-09T15:29:41+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -555,7 +555,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-06T09:15:11+00:00</t>
+          <t>2026-10-09T15:29:41+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -586,7 +586,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-06T09:15:11+00:00</t>
+          <t>2026-10-09T15:29:41+00:00</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -617,7 +617,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-06T09:15:11+00:00</t>
+          <t>2026-10-09T15:29:41+00:00</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-06T09:15:11+00:00</t>
+          <t>2026-10-09T15:29:41+00:00</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -679,7 +679,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-06T09:15:11+00:00</t>
+          <t>2026-10-09T15:29:41+00:00</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -710,7 +710,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-06T09:15:11+00:00</t>
+          <t>2026-10-09T15:29:41+00:00</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-06T09:15:11+00:00</t>
+          <t>2026-10-09T15:29:41+00:00</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-06T09:15:11+00:00</t>
+          <t>2026-10-09T15:29:41+00:00</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -803,7 +803,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-06T09:15:11+00:00</t>
+          <t>2026-10-09T15:29:41+00:00</t>
         </is>
       </c>
       <c r="D12" t="n">
